--- a/Proyecto Interno/review-food-security-paper/07_tables/final/tab01_cost_annual.xlsx
+++ b/Proyecto Interno/review-food-security-paper/07_tables/final/tab01_cost_annual.xlsx
@@ -6,16 +6,17 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="A. Costs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B. Premiums" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="A. Nominal costs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="B. Real costs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="C. Premiums" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
-  <si>
-    <t xml:space="preserve">Table 1A. Mean real per capita daily diet costs (real COP/day, base: December 2018)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
+  <si>
+    <t xml:space="preserve">Table 1A. Mean nominal per capita daily diet costs (COP/day)</t>
   </si>
   <si>
     <t xml:space="preserve">City</t>
@@ -39,6 +40,225 @@
     <t xml:space="preserve">2019–2024</t>
   </si>
   <si>
+    <t xml:space="preserve">2,083 (380)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,020 (909)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,135 (1,449)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,717 (16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,961 (57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,436 (116)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,760 (18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,181 (55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,866 (100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,810 (80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,404 (122)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,125 (191)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,295 (237)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,324 (365)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,548 (564)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,707 (174)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,116 (69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,846 (136)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,207 (86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,136 (42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,989 (120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medellín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,027 (364)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,189 (919)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,948 (1,341)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,672 (23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,087 (70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,333 (78)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,689 (17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,335 (72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,724 (110)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,774 (62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,574 (155)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,039 (229)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,201 (203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,577 (352)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,527 (534)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,628 (113)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,278 (55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,496 (157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,200 (81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,281 (55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,567 (115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,013 (353)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,195 (982)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,018 (1,435)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,646 (20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,029 (68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,317 (81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,708 (24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,286 (56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,727 (91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,805 (61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,548 (157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,053 (189)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,230 (207)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,547 (362)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,478 (529)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,595 (148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,431 (109)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,736 (230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,092 (101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,327 (81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,797 (114)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: Mean (standard deviation) across monthly observations. Real COP deflated by city-level food CPI (DANE División 01100000, base: December 2018).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1B. Mean real per capita daily diet costs (real COP/day, base: December 2018)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,507 (146)</t>
   </si>
   <si>
@@ -48,9 +268,6 @@
     <t xml:space="preserve">4,366 (129)</t>
   </si>
   <si>
-    <t xml:space="preserve">2019</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,640 (18)</t>
   </si>
   <si>
@@ -60,9 +277,6 @@
     <t xml:space="preserve">4,236 (57)</t>
   </si>
   <si>
-    <t xml:space="preserve">2020</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,598 (21)</t>
   </si>
   <si>
@@ -72,9 +286,6 @@
     <t xml:space="preserve">4,418 (24)</t>
   </si>
   <si>
-    <t xml:space="preserve">2021</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,495 (27)</t>
   </si>
   <si>
@@ -84,9 +295,6 @@
     <t xml:space="preserve">4,234 (58)</t>
   </si>
   <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,514 (77)</t>
   </si>
   <si>
@@ -96,9 +304,6 @@
     <t xml:space="preserve">4,323 (126)</t>
   </si>
   <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,561 (110)</t>
   </si>
   <si>
@@ -108,9 +313,6 @@
     <t xml:space="preserve">4,522 (72)</t>
   </si>
   <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,234 (61)</t>
   </si>
   <si>
@@ -120,9 +322,6 @@
     <t xml:space="preserve">4,462 (18)</t>
   </si>
   <si>
-    <t xml:space="preserve">Medellín</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,460 (123)</t>
   </si>
   <si>
@@ -186,9 +385,6 @@
     <t xml:space="preserve">4,237 (44)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cali</t>
-  </si>
-  <si>
     <t xml:space="preserve">1,397 (151)</t>
   </si>
   <si>
@@ -252,10 +448,7 @@
     <t xml:space="preserve">4,120 (40)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: Mean (standard deviation) across monthly observations. Real COP deflated by city-level food CPI (DANE División 01100000, base: December 2018).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 1B. Nutritional quality premiums (cost ratios)</t>
+    <t xml:space="preserve">Table 1C. Nutritional quality premiums (cost ratios, adimensional)</t>
   </si>
   <si>
     <t xml:space="preserve">CoNA/CoCA</t>
@@ -1281,13 +1474,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1298,13 +1491,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -1315,13 +1508,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -1332,13 +1525,13 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -1349,13 +1542,13 @@
         <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -1366,13 +1559,13 @@
         <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -1383,13 +1576,13 @@
         <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9">
@@ -1400,13 +1593,13 @@
         <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -1417,13 +1610,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -1434,13 +1627,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -1451,13 +1644,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -1468,13 +1661,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
@@ -1485,13 +1678,13 @@
         <v>23</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1502,13 +1695,13 @@
         <v>27</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1519,13 +1712,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -1536,13 +1729,13 @@
         <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -1553,13 +1746,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
@@ -1570,13 +1763,13 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20">
@@ -1587,13 +1780,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -1604,13 +1797,13 @@
         <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
@@ -1621,13 +1814,13 @@
         <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
@@ -1638,13 +1831,419 @@
         <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>144</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="D23" s="3" t="s">
-        <v>145</v>
+        <v>209</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>146</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1">
